--- a/data/trans_orig/IP18A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18A01-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14255</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>26874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>28387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32269</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50587</t>
+          <t>51808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74542</t>
+          <t>74840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87459</t>
+          <t>87135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79196</t>
+          <t>79294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92479</t>
+          <t>92526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158808</t>
+          <t>157587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177126</t>
+          <t>176218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>26753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44602</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208834</t>
+          <t>209011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221420</t>
+          <t>221185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207552</t>
+          <t>207469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220849</t>
+          <t>220948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>420387</t>
+          <t>419486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>438025</t>
+          <t>438236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17550</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95741</t>
+          <t>95163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103522</t>
+          <t>103415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105370</t>
+          <t>105066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112963</t>
+          <t>112955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204151</t>
+          <t>204350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214997</t>
+          <t>215407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23685</t>
+          <t>23999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143072</t>
+          <t>142971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153373</t>
+          <t>153403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155043</t>
+          <t>154739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163851</t>
+          <t>163631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302262</t>
+          <t>301948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315172</t>
+          <t>315601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62606</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41419</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64291</t>
+          <t>64459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87795</t>
+          <t>88837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118659</t>
+          <t>120141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535412</t>
+          <t>534320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>557018</t>
+          <t>555849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>559723</t>
+          <t>559555</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>582595</t>
+          <t>582366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1103373</t>
+          <t>1101891</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1134237</t>
+          <t>1133195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45351</t>
+          <t>45307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27050</t>
+          <t>28180</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45129</t>
+          <t>45747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60821</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84527</t>
+          <t>85486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96220</t>
+          <t>96264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113544</t>
+          <t>113278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96467</t>
+          <t>95849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114546</t>
+          <t>113416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198640</t>
+          <t>197681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222346</t>
+          <t>222881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,71%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>24224</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31754</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>31161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>51110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195455</t>
+          <t>195626</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209537</t>
+          <t>208820</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220904</t>
+          <t>221481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236707</t>
+          <t>237539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422627</t>
+          <t>421397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441800</t>
+          <t>441346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136829</t>
+          <t>136623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146248</t>
+          <t>146477</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139693</t>
+          <t>139245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147930</t>
+          <t>147725</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280481</t>
+          <t>279908</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>293260</t>
+          <t>292183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18159</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142843</t>
+          <t>143097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150517</t>
+          <t>150567</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150960</t>
+          <t>150958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159881</t>
+          <t>159958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>297744</t>
+          <t>298702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308826</t>
+          <t>309423</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>77796</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57925</t>
+          <t>58366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84753</t>
+          <t>85503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118617</t>
+          <t>119009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156587</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>586002</t>
+          <t>586008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>610925</t>
+          <t>609881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>622908</t>
+          <t>622158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>649736</t>
+          <t>649295</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1214878</t>
+          <t>1215646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1252848</t>
+          <t>1252456</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37650</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32915</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46215</t>
+          <t>44721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66892</t>
+          <t>66436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89359</t>
+          <t>88816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104224</t>
+          <t>103721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84903</t>
+          <t>84124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99375</t>
+          <t>98567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177936</t>
+          <t>178392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198613</t>
+          <t>200107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27499</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23977</t>
+          <t>23032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41813</t>
+          <t>40803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173423</t>
+          <t>173807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184506</t>
+          <t>184391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208749</t>
+          <t>209453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223308</t>
+          <t>223445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386503</t>
+          <t>387513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>404339</t>
+          <t>405284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157489</t>
+          <t>157385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166196</t>
+          <t>165703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155516</t>
+          <t>156245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165034</t>
+          <t>165092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316727</t>
+          <t>316576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329437</t>
+          <t>329262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132932</t>
+          <t>133364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144283</t>
+          <t>144621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135396</t>
+          <t>135777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144322</t>
+          <t>143966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>272754</t>
+          <t>272601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287237</t>
+          <t>287003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>49014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73365</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70654</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>102758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138204</t>
+          <t>135141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>566980</t>
+          <t>566263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>592284</t>
+          <t>591331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>596921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622317</t>
+          <t>621728</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1171821</t>
+          <t>1174884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1207281</t>
+          <t>1207267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>800</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>15175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26109</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32174</t>
+          <t>32322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24357</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29547</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56124</t>
+          <t>56366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61322</t>
+          <t>61337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>30894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62846</t>
+          <t>62654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67786</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19312</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37296</t>
+          <t>37234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58614</t>
+          <t>59839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66180</t>
+          <t>66284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87670</t>
+          <t>87530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96679</t>
+          <t>96545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122152</t>
+          <t>121587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129056</t>
+          <t>129063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213034</t>
+          <t>213304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223728</t>
+          <t>224190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18A01-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21144</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15135</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28351</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>20099</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14579</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26874</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14633</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>15155</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28387</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33177</t>
+          <t>33200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51808</t>
+          <t>51567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79330</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>92546</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>81615</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74840</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>87135</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>74673</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87081</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,24%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86537</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79294</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>92526</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157587</t>
+          <t>157828</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176218</t>
+          <t>176195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>107681</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>101714</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>107681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18571</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13030</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26160</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16080</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10401</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22575</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10495</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22980</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18571</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12454</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>25933</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45503</t>
+          <t>44154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>214831</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>207242</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>220372</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>215506</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>209011</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>221185</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>208606</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>221091</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>214831</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>207469</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>220948</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>419486</t>
+          <t>420835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>438236</t>
+          <t>438763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>233402</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>231586</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>233402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9741</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>5615</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2615</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10867</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5499</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2716</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10605</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>110172</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105930</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>112950</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>100415</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>95163</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>103415</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>95626</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>103388</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>110172</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>105066</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>112955</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204350</t>
+          <t>204596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215407</t>
+          <t>214997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>115671</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>106030</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>115671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6972</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9333</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5284</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15716</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5308</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15375</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6972</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3629</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>23209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>160288</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>155284</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>163761</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>149354</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>142971</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153403</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>143312</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>153379</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>160288</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>154739</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>163631</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301948</t>
+          <t>302738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315601</t>
+          <t>315555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167260</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>158687</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>167260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41097</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63437</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>51127</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>42169</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>63698</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>40701</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>62933</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>52186</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>41648</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>64459</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88837</t>
+          <t>87981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120141</t>
+          <t>121498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>571828</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>560577</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>582917</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>815</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>546891</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>534320</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>555849</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>535085</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>557317</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,45%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>861</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>571828</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>559555</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>582366</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1101891</t>
+          <t>1100534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1133195</t>
+          <t>1134051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>624014</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>624014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2012 (tasa de respuesta: 98,1%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2012 (tasa de respuesta: 98,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36211</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28248</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46010</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35939</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28293</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45307</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>27637</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>43873</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>36211</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28180</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>45747</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60286</t>
+          <t>61426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85486</t>
+          <t>85173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>105385</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>95586</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>113348</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>74,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>105632</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>96264</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>113278</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>97698</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>113934</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>74,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>68,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>105385</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>95849</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>113416</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>74,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197681</t>
+          <t>197994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222881</t>
+          <t>221741</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>141596</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>141596</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>141596</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>141571</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>141571</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>141571</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>141596</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>141596</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>141596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22816</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16141</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31575</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16939</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11030</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24224</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11549</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24783</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22816</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15119</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>31177</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>50872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>229842</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>221083</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>236517</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>292</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>202911</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>195626</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>208820</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>195067</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>208301</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>229842</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>221481</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>237539</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>421397</t>
+          <t>421635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441346</t>
+          <t>441532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252658</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252658</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252658</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>219850</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>219850</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>219850</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252658</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252658</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252658</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7845</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13591</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13486</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,22%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10429</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>145080</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>139597</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>147727</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>142369</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>136623</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>146477</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>136728</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>146657</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>145080</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>139245</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>147725</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>279908</t>
+          <t>279515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>292183</t>
+          <t>292832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149674</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150214</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,107 +3699,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7198</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3760</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12515</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4386</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1603</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9073</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9490</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>11584</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>6465</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>18836</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7198</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12776</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>11584</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>6480</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>17201</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3812,102 +3812,102 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156536</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>151219</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>159974</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>147784</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>143097</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>150567</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>142680</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>150249</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>304319</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>297067</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>309438</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>96,33%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>94,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>156536</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>150958</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>159958</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>304319</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>298702</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>309423</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163734</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163734</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163734</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>152170</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>163734</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>163734</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>163734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>70819</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58462</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>87104</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>65108</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53923</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>77796</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>52968</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>78747</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>70819</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>58366</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>85503</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119009</t>
+          <t>118088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155819</t>
+          <t>153873</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>636842</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>620557</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>649199</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>862</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>598696</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>586008</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>609881</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>585057</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>610836</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>636842</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>622158</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>649295</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1215646</t>
+          <t>1217592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1252456</t>
+          <t>1253377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>707661</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>707661</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>707661</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>955</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>663804</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>663804</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>663804</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>707661</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>707661</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>707661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2016 (tasa de respuesta: 98,16%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2016 (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25559</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18319</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33038</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29573</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23288</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38193</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22263</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37165</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>23,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25559</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19251</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33694</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>92259</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>84780</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>99499</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>97436</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>88816</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>103721</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>89844</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>104746</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>76,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>92259</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>84124</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>98567</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178392</t>
+          <t>179876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200107</t>
+          <t>200163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>117818</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>127009</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>117818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19733</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13875</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27971</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11805</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>7677</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18261</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18511</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19733</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12803</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26795</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23032</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40803</t>
+          <t>41146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>216515</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>208277</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>222373</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>180263</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>173807</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>173557</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>184391</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>96,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>216515</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>209453</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>223445</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,65%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>88,66%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>604</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>387513</t>
+          <t>387170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>405284</t>
+          <t>404631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236248</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>192068</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>192068</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>192068</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>236248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7356</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6967</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3795</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12113</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3621</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11892</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,11%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7356</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3675</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12522</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>161411</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155660</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165077</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>162531</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>157385</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>165703</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>157606</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>165877</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>161411</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>156245</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165092</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316576</t>
+          <t>316628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329262</t>
+          <t>329000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168767</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168767</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168767</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>169498</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>168767</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>168767</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>168767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11421</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11902</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7148</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18405</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6878</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5974</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2881</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11070</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>140873</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135426</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>143844</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>139867</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>133364</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>144621</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>133588</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>144891</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>140873</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>135777</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>143966</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>272601</t>
+          <t>272415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287003</t>
+          <t>286818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>146847</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>146847</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>146847</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151769</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151769</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151769</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>146847</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>146847</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>146847</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45971</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72075</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>60248</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49014</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74082</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>72997</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>58621</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>47953</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>72760</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102758</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135141</t>
+          <t>137035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>611060</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>597606</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>623710</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>877</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>580097</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>566263</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>591331</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>567348</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>590682</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,59%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>611060</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>596921</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>621728</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1174884</t>
+          <t>1172990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1207267</t>
+          <t>1206442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>640345</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4077</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2748</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5517</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13551</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11275</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,27%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13547</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10778</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15175</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,15%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>26286</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26435</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16295</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34742</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3401</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3677</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1541</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4122</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27921</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25745</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28857</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>27435</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24379</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>24666</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21723</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25400</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>85,52%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>32187</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>29606</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>33343</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,78%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>92</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>59621</t>
+          <t>52587</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56366</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61337</t>
+          <t>54067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>29146</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28198</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61925</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6003</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>29348</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30894</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>27572</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>66219</t>
+          <t>63135</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62654</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67787</t>
+          <t>64771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35563</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>29554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68167</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40138</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36244</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>22825</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19505</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>23699</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19973</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25490</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>92,97%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>78,35%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>41045</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>37234</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>42546</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>87,51%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>86</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>63869</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>59447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66284</t>
+          <t>66204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>24526</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>25490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2282</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8806</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3769</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12784</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18602</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117173</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>112916</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>119440</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>93154</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>87530</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>96545</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126249</t>
+          <t>88674</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121587</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129063</t>
+          <t>92214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>219403</t>
+          <t>205847</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213304</t>
+          <t>199349</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>224190</t>
+          <t>209948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
